--- a/Тест2/257.xlsx
+++ b/Тест2/257.xlsx
@@ -210,22 +210,22 @@
     <t xml:space="preserve">Yo'llanma xatga nimalar yoziladi?</t>
   </si>
   <si>
-    <t xml:space="preserve">Olingan vaqt, mahsulot nomi, partiya raqami, sana</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Idish rangi, hajmi va vazni</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Iste'molchi yoshi, jinsi, kasbi</t>
+    <t xml:space="preserve">Vaqt, mahsulot nomi, partiya raqami, sana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Idish rangi, hajmi va vazni, shakli</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Iste'molchi yoshi, jinsi, kasbi, manzili</t>
   </si>
   <si>
     <t xml:space="preserve">Sotuvchi ismi, mahsulot narxi, chegirma</t>
   </si>
   <si>
-    <t xml:space="preserve">Xarid joyi, kassir va chek</t>
-  </si>
-  <si>
-    <t xml:space="preserve">To'g'ri javob: Olingan vaqt, mahsulot nomi, partiya raqami, sana. Namuna olish vaqti, mahsulot nomi, partiya raqami va ishlab chiqarilgan sana yo'llanma xatga yoziladi. Manba: Mavzu materiali (257.docx).</t>
+    <t xml:space="preserve">Xarid joyi, kassir ismi va chek raqami</t>
+  </si>
+  <si>
+    <t xml:space="preserve">To'g'ri javob: Vaqt, mahsulot nomi, partiya raqami, sana. Namuna olish vaqti, mahsulot nomi, partiya raqami va ishlab chiqarilgan sana yo'llanma xatga yoziladi. Manba: Mavzu materiali (257.docx).</t>
   </si>
   <si>
     <t xml:space="preserve">Ichimlikda koliformlar topilsa nimani bildiradi?</t>
@@ -285,7 +285,7 @@
     <t xml:space="preserve">Tiniqlashtirib beradi</t>
   </si>
   <si>
-    <t xml:space="preserve">Sterilligini oshiradi</t>
+    <t xml:space="preserve">Sterilligini oshirib beradi</t>
   </si>
   <si>
     <t xml:space="preserve">To'g'ri javob: Ta'mi, hidi va ko'rinishini buzadi. Xamirturush va mog'orlar kislotali muhitda yaxshi o'sib, mahsulotning ta'mi, hidi va ko'rinishini buzadi. Manba: Mavzu materiali (257.docx).</t>
